--- a/limesurvey_survey_builder.xlsx
+++ b/limesurvey_survey_builder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d25bc81654746e6/GitHub/limesurvey-excel-builder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_81CD780B6FE431C4565093A94BF2E0DE1051590A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07E3CECB-CA2E-429E-A36C-4A19D019125D}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_494C36BC3916FC6A191B0AEA44B9CB41A68BF5D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{310454CF-6682-4E7A-89EB-09C22C13AACD}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,6 +23,45 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>limesurvey-excel-builder</author>
+  </authors>
+  <commentList>
+    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>AUTO-MANAGED: The R script now detects the base language from the first text_xx column (e.g. text_en → 'en'). This value is overwritten automatically on each run. You do not need to edit it manually.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>AUTO-MANAGED: The R script detects additional languages from the remaining text_xx columns (e.g. text_ro, text_fr, text_es → 'ro fr es') in column order. This value is overwritten automatically on each run. You do not need to edit it manually.
+To add a language: insert a text_xx column (and optionally help_xx) in the Survey Design sheet. The script will pick it up automatically.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="1142">
   <si>
@@ -3205,7 +3244,7 @@
     <t>2. For translations: add text_fr, help_fr, text_de, help_de columns (next to text_en, help_en)</t>
   </si>
   <si>
-    <t>3. Set the S row additional_languages (e.g. text=fr de) to declare extra languages</t>
+    <t>3. Languages are auto-detected from text_xx column names — no manual settings needed</t>
   </si>
   <si>
     <t>4. Format text freely in Excel: bold, italic, underline, colors are detected and converted to HTML</t>
@@ -3235,7 +3274,7 @@
     <t xml:space="preserve">  1. Insert new columns after help_en, named text_fr and help_fr (or text_de, help_de, etc.)</t>
   </si>
   <si>
-    <t xml:space="preserve">  2. Add an S row: name=additional_languages, text_en=fr (or fr de for multiple)</t>
+    <t xml:space="preserve">  2. The R script auto-detects the new language from the column name — no S rows to add</t>
   </si>
   <si>
     <t xml:space="preserve">  3. Add SL rows with text_fr filled in (surveyls_title, surveyls_description, etc.)</t>
@@ -3244,7 +3283,7 @@
     <t xml:space="preserve">  4. Fill in text_fr for all G, Q, SQ, A rows. help_fr is optional.</t>
   </si>
   <si>
-    <t xml:space="preserve">  5. Leave text_fr empty for S rows (settings are language-independent).</t>
+    <t xml:space="preserve">  5. Leave text_xx empty for S rows — settings are language-independent and HTML formatting is never applied to S rows.</t>
   </si>
   <si>
     <t>COLOR CODING (automatic via conditional formatting)</t>
@@ -3409,7 +3448,9 @@
     <t>The R script reads all text_xx/help_xx columns and generates multi-language TSV output.</t>
   </si>
   <si>
-    <t>For S rows: only text_en is used (settings are language-independent).</t>
+    <t>For S rows: only text_en is used (settings are language-independent). Rich text formatting
+    (bold, color, underline) is always ignored for S rows — plain text only. This prevents
+    import errors from LibreOffice auto-formatting (e.g. email addresses as hyperlinks).</t>
   </si>
   <si>
     <t>For SL rows: fill text_xx for each language (title, description, welcome, end text).</t>
@@ -3461,7 +3502,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3589,6 +3630,12 @@
       <color theme="2" tint="-0.749992370372631"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0563C1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="9">
@@ -3723,7 +3770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3815,11 +3862,14 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3836,50 +3886,8 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF8BE5B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
+        <patternFill>
           <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2AE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFB9F1D1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4201,7 +4209,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BI181"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4551,7 +4559,7 @@
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="33" t="s">
         <v>65</v>
       </c>
       <c r="K4" s="14"/>
@@ -18271,22 +18279,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:BH100000">
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="5" priority="9">
       <formula>$C2="S"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="4" priority="10">
       <formula>$C2="SL"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="3" priority="11">
       <formula>$C2="G"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="12">
+    <cfRule type="expression" dxfId="2" priority="12">
       <formula>$C2="Q"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="13">
+    <cfRule type="expression" dxfId="1" priority="13">
       <formula>$C2="SQ"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="14">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>$C2="A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18303,6 +18311,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/limesurvey_survey_builder.xlsx
+++ b/limesurvey_survey_builder.xlsx
@@ -14253,7 +14253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="22.73046875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -14293,40 +14293,50 @@
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
+          <t>quota_url</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>quota_url_description</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
           <t>message_en</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>message_ro</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>message_fr</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>message_es</t>
         </is>
       </c>
-      <c r="J1" s="14" t="inlineStr">
+      <c r="L1" s="14" t="inlineStr">
         <is>
           <t>question_code_1</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
+      <c r="M1" s="14" t="inlineStr">
         <is>
           <t>answer_code_1</t>
         </is>
       </c>
-      <c r="L1" s="14" t="inlineStr">
+      <c r="N1" s="14" t="inlineStr">
         <is>
           <t>question_code_2</t>
         </is>
       </c>
-      <c r="M1" s="14" t="inlineStr">
+      <c r="O1" s="14" t="inlineStr">
         <is>
           <t>answer_code_2</t>
         </is>
@@ -14358,42 +14368,47 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://example.com/survey-complete</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>This quota is now complete. Thank you for your interest.</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Aceasta cota este acum completa. Va multumim pentru interes.</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Ce quota est maintenant complet. Merci de votre interet.</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Esta cuota esta completa. Gracias por su interes.</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -14425,42 +14440,47 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://example.com/survey-complete</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>This quota is now complete. Thank you for your interest.</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Aceasta cota este acum completa. Va multumim pentru interes.</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Ce quota est maintenant complet. Merci de votre interet.</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Esta cuota esta completa. Gracias por su interes.</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -14492,42 +14512,47 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://example.com/survey-complete</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>This quota is now complete. Thank you for your interest.</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Aceasta cota este acum completa. Va multumim pentru interes.</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Ce quota est maintenant complet. Merci de votre interet.</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Esta cuota esta completa. Gracias por su interes.</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -14559,42 +14584,47 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://example.com/survey-complete</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>This quota is now complete. Thank you for your interest.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Aceasta cota este acum completa. Va multumim pentru interes.</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Ce quota est maintenant complet. Merci de votre interet.</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Esta cuota esta completa. Gracias por su interes.</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -14626,42 +14656,47 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://example.com/survey-complete</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>This quota is now complete. Thank you for your interest.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Aceasta cota este acum completa. Va multumim pentru interes.</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Ce quota est maintenant complet. Merci de votre interet.</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Esta cuota esta completa. Gracias por su interes.</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -14693,42 +14728,47 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://example.com/survey-complete</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>This quota is now complete. Thank you for your interest.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Aceasta cota este acum completa. Va multumim pentru interes.</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Ce quota est maintenant complet. Merci de votre interet.</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Esta cuota esta completa. Gracias por su interes.</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>S</t>
         </is>
